--- a/output/pdf_financials_xlsx/SUN.xlsx
+++ b/output/pdf_financials_xlsx/SUN.xlsx
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000326</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.01226</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008344000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.561419</v>
+        <v>-0.561745</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.423968</v>
+        <v>-5.436228</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.602134</v>
+        <v>-2.610478</v>
       </c>
     </row>
     <row r="28">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.498282</v>
+        <v>-0.498608</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.351517</v>
+        <v>-5.363777</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.491213</v>
+        <v>-2.499557</v>
       </c>
     </row>
     <row r="30">
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-18.88283691619969</v>
+        <v>-18.89519097441308</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-148.1234617518011</v>
+        <v>-148.4628035946985</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-53.39572947848128</v>
+        <v>-53.57457165968717</v>
       </c>
     </row>
     <row r="31">
@@ -3744,13 +3744,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06840300000000001</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.06840300000000001</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.093366</v>
       </c>
     </row>
     <row r="125">
@@ -3769,13 +3769,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06840300000000001</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.06840300000000001</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.093366</v>
       </c>
     </row>
     <row r="126">
@@ -7186,7 +7186,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -10566,7 +10570,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">

--- a/output/pdf_financials_xlsx/SUN.xlsx
+++ b/output/pdf_financials_xlsx/SUN.xlsx
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.013617</v>
+        <v>0.013617</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.005583</v>
+        <v>-0.004914</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0.104385</v>
+        <v>0.092699</v>
       </c>
     </row>
     <row r="18">
@@ -1360,10 +1360,10 @@
         <v>-2.425461197430083</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.102932023197777</v>
+        <v>-0.09059787963350817</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-4.011515164092241</v>
+        <v>-3.562422227294982</v>
       </c>
     </row>
     <row r="32">
@@ -3413,13 +3413,13 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000257</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008521000000000001</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006724</v>
       </c>
     </row>
     <row r="112">
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.01514</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000257</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008521000000000001</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006724</v>
       </c>
     </row>
     <row r="135">
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.23121</v>
+        <v>-0.231467</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.107678</v>
+        <v>-1.116199</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-2.511685</v>
+        <v>-2.518409</v>
       </c>
     </row>
   </sheetData>
@@ -6960,7 +6960,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7458,7 +7462,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -8276,7 +8284,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -10888,7 +10900,11 @@
           <t>Current income tax recovery (expense) (note 15)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -10930,7 +10946,11 @@
           <t>Deferred income tax recovery (expense) (note 15)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -11884,7 +11904,11 @@
           <t>Deferred income tax recovery (note 15)</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
